--- a/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_85.xlsx
+++ b/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_85.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\LApredict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622AC956-F9F1-4FF4-A018-2D29974651EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E39F60C-B517-4954-B289-F633C0D61537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27540" yWindow="6630" windowWidth="24910" windowHeight="14110" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="valid" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">valid!$A$2:$P$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>Total Rows</t>
   </si>
@@ -84,9 +85,6 @@
   </si>
   <si>
     <t>recall fault-prone</t>
-  </si>
-  <si>
-    <t>Test avg</t>
   </si>
   <si>
     <t>Valid avg</t>
@@ -146,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -154,6 +152,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -3957,15 +3956,15 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="N67">
-        <f t="shared" ref="N67:N98" si="6">H67/B67</f>
+        <f t="shared" ref="N67:N102" si="6">H67/B67</f>
         <v>0.70461538461538464</v>
       </c>
       <c r="O67">
-        <f t="shared" ref="O67:O98" si="7">I67/C67</f>
+        <f t="shared" ref="O67:O102" si="7">I67/C67</f>
         <v>0.71841609050911381</v>
       </c>
       <c r="P67">
-        <f t="shared" ref="P67:P98" si="8">J67/D67</f>
+        <f t="shared" ref="P67:P102" si="8">J67/D67</f>
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
@@ -5506,7 +5505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1913</v>
       </c>
@@ -5559,7 +5558,7 @@
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1913</v>
       </c>
@@ -5612,7 +5611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1913</v>
       </c>
@@ -5653,19 +5652,19 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="N99">
-        <f t="shared" ref="N99:N112" si="9">H99/B99</f>
+        <f t="shared" si="6"/>
         <v>0.69372693726937273</v>
       </c>
       <c r="O99">
-        <f t="shared" ref="O99:O112" si="10">I99/C99</f>
+        <f t="shared" si="7"/>
         <v>0.70880503144654083</v>
       </c>
       <c r="P99">
-        <f t="shared" ref="P99:P112" si="11">J99/D99</f>
+        <f t="shared" si="8"/>
         <v>2.7777777777777776E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1913</v>
       </c>
@@ -5706,19 +5705,19 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="N100">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>0.66564792176039123</v>
       </c>
       <c r="O100">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0.67788161993769469</v>
       </c>
       <c r="P100">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1913</v>
       </c>
@@ -5759,19 +5758,19 @@
         <v>0</v>
       </c>
       <c r="N101">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>0.69160024524831387</v>
       </c>
       <c r="O101">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0.70721003134796234</v>
       </c>
       <c r="P101">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1913</v>
       </c>
@@ -5812,684 +5811,85 @@
         <v>0</v>
       </c>
       <c r="N102">
+        <f t="shared" si="6"/>
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="O102">
+        <f t="shared" si="7"/>
+        <v>0.69962686567164178</v>
+      </c>
+      <c r="P102">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <f t="shared" ref="A105:P105" si="9">AVERAGE(A3:A102)</f>
+        <v>1912.9</v>
+      </c>
+      <c r="B105">
         <f t="shared" si="9"/>
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="O102">
-        <f t="shared" si="10"/>
-        <v>0.69962686567164178</v>
-      </c>
-      <c r="P102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>4783</v>
-      </c>
-      <c r="B103">
-        <v>4048</v>
-      </c>
-      <c r="C103">
-        <v>3997</v>
-      </c>
-      <c r="D103">
-        <v>51</v>
-      </c>
-      <c r="E103">
-        <v>3089</v>
-      </c>
-      <c r="F103">
-        <v>3085</v>
-      </c>
-      <c r="G103">
-        <v>4</v>
-      </c>
-      <c r="H103">
-        <v>2785</v>
-      </c>
-      <c r="I103">
-        <v>2784</v>
-      </c>
-      <c r="J103">
-        <v>1</v>
-      </c>
-      <c r="K103">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L103">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M103">
-        <v>0.25</v>
-      </c>
-      <c r="N103">
+        <v>1616.5</v>
+      </c>
+      <c r="C105">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O103">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P103">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>4783</v>
-      </c>
-      <c r="B104">
-        <v>4048</v>
-      </c>
-      <c r="C104">
-        <v>3997</v>
-      </c>
-      <c r="D104">
-        <v>51</v>
-      </c>
-      <c r="E104">
-        <v>3089</v>
-      </c>
-      <c r="F104">
-        <v>3085</v>
-      </c>
-      <c r="G104">
-        <v>4</v>
-      </c>
-      <c r="H104">
-        <v>2785</v>
-      </c>
-      <c r="I104">
-        <v>2784</v>
-      </c>
-      <c r="J104">
-        <v>1</v>
-      </c>
-      <c r="K104">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L104">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M104">
-        <v>0.25</v>
-      </c>
-      <c r="N104">
+        <v>1589.34</v>
+      </c>
+      <c r="D105">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O104">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P104">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>4783</v>
-      </c>
-      <c r="B105">
-        <v>4048</v>
-      </c>
-      <c r="C105">
-        <v>3997</v>
-      </c>
-      <c r="D105">
-        <v>51</v>
+        <v>27.16</v>
       </c>
       <c r="E105">
-        <v>3089</v>
+        <f t="shared" si="9"/>
+        <v>1246.8900000000001</v>
       </c>
       <c r="F105">
-        <v>3085</v>
+        <f t="shared" si="9"/>
+        <v>1245.1500000000001</v>
       </c>
       <c r="G105">
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>1.74</v>
       </c>
       <c r="H105">
-        <v>2785</v>
+        <f t="shared" si="9"/>
+        <v>1128.23</v>
       </c>
       <c r="I105">
-        <v>2784</v>
+        <f t="shared" si="9"/>
+        <v>1127.3399999999999</v>
       </c>
       <c r="J105">
-        <v>1</v>
-      </c>
-      <c r="K105">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L105">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M105">
-        <v>0.25</v>
-      </c>
-      <c r="N105">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O105">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P105">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>4783</v>
-      </c>
-      <c r="B106">
-        <v>4048</v>
-      </c>
-      <c r="C106">
-        <v>3997</v>
-      </c>
-      <c r="D106">
-        <v>51</v>
-      </c>
-      <c r="E106">
-        <v>3089</v>
-      </c>
-      <c r="F106">
-        <v>3085</v>
-      </c>
-      <c r="G106">
-        <v>4</v>
-      </c>
-      <c r="H106">
-        <v>2785</v>
-      </c>
-      <c r="I106">
-        <v>2784</v>
-      </c>
-      <c r="J106">
-        <v>1</v>
-      </c>
-      <c r="K106">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L106">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M106">
-        <v>0.25</v>
-      </c>
-      <c r="N106">
+        <v>0.89</v>
+      </c>
+      <c r="K105" s="3">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O106">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P106">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>4783</v>
-      </c>
-      <c r="B107">
-        <v>4048</v>
-      </c>
-      <c r="C107">
-        <v>3997</v>
-      </c>
-      <c r="D107">
-        <v>51</v>
-      </c>
-      <c r="E107">
-        <v>3089</v>
-      </c>
-      <c r="F107">
-        <v>3085</v>
-      </c>
-      <c r="G107">
-        <v>4</v>
-      </c>
-      <c r="H107">
-        <v>2785</v>
-      </c>
-      <c r="I107">
-        <v>2784</v>
-      </c>
-      <c r="J107">
-        <v>1</v>
-      </c>
-      <c r="K107">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L107">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M107">
-        <v>0.25</v>
-      </c>
-      <c r="N107">
+        <v>0.90489731188596967</v>
+      </c>
+      <c r="L105" s="3">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O107">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P107">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>4783</v>
-      </c>
-      <c r="B108">
-        <v>4048</v>
-      </c>
-      <c r="C108">
-        <v>3997</v>
-      </c>
-      <c r="D108">
-        <v>51</v>
-      </c>
-      <c r="E108">
-        <v>3089</v>
-      </c>
-      <c r="F108">
-        <v>3085</v>
-      </c>
-      <c r="G108">
-        <v>4</v>
-      </c>
-      <c r="H108">
-        <v>2785</v>
-      </c>
-      <c r="I108">
-        <v>2784</v>
-      </c>
-      <c r="J108">
-        <v>1</v>
-      </c>
-      <c r="K108">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L108">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M108">
-        <v>0.25</v>
-      </c>
-      <c r="N108">
+        <v>0.90544552828692626</v>
+      </c>
+      <c r="M105" s="3">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O108">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P108">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>4783</v>
-      </c>
-      <c r="B109">
-        <v>4088</v>
-      </c>
-      <c r="C109">
-        <v>4063</v>
-      </c>
-      <c r="D109">
-        <v>25</v>
-      </c>
-      <c r="E109">
-        <v>3089</v>
-      </c>
-      <c r="F109">
-        <v>3085</v>
-      </c>
-      <c r="G109">
-        <v>4</v>
-      </c>
-      <c r="H109">
-        <v>2785</v>
-      </c>
-      <c r="I109">
-        <v>2784</v>
-      </c>
-      <c r="J109">
-        <v>1</v>
-      </c>
-      <c r="K109">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L109">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M109">
-        <v>0.25</v>
-      </c>
-      <c r="N109">
+        <v>0.40016666666666673</v>
+      </c>
+      <c r="N105" s="3">
         <f t="shared" si="9"/>
-        <v>0.68126223091976512</v>
-      </c>
-      <c r="O109">
-        <f t="shared" si="10"/>
-        <v>0.6852079744031504</v>
-      </c>
-      <c r="P109">
-        <f t="shared" si="11"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>4783</v>
-      </c>
-      <c r="B110">
-        <v>4048</v>
-      </c>
-      <c r="C110">
-        <v>3997</v>
-      </c>
-      <c r="D110">
-        <v>51</v>
-      </c>
-      <c r="E110">
-        <v>3089</v>
-      </c>
-      <c r="F110">
-        <v>3085</v>
-      </c>
-      <c r="G110">
-        <v>4</v>
-      </c>
-      <c r="H110">
-        <v>2785</v>
-      </c>
-      <c r="I110">
-        <v>2784</v>
-      </c>
-      <c r="J110">
-        <v>1</v>
-      </c>
-      <c r="K110">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L110">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M110">
-        <v>0.25</v>
-      </c>
-      <c r="N110">
+        <v>0.69798167731187843</v>
+      </c>
+      <c r="O105" s="3">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O110">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P110">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>4783</v>
-      </c>
-      <c r="B111">
-        <v>4048</v>
-      </c>
-      <c r="C111">
-        <v>3997</v>
-      </c>
-      <c r="D111">
-        <v>51</v>
-      </c>
-      <c r="E111">
-        <v>3089</v>
-      </c>
-      <c r="F111">
-        <v>3085</v>
-      </c>
-      <c r="G111">
-        <v>4</v>
-      </c>
-      <c r="H111">
-        <v>2785</v>
-      </c>
-      <c r="I111">
-        <v>2784</v>
-      </c>
-      <c r="J111">
-        <v>1</v>
-      </c>
-      <c r="K111">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L111">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M111">
-        <v>0.25</v>
-      </c>
-      <c r="N111">
+        <v>0.70936400714902093</v>
+      </c>
+      <c r="P105" s="3">
         <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O111">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P111">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>4783</v>
-      </c>
-      <c r="B112">
-        <v>4048</v>
-      </c>
-      <c r="C112">
-        <v>3997</v>
-      </c>
-      <c r="D112">
-        <v>51</v>
-      </c>
-      <c r="E112">
-        <v>3089</v>
-      </c>
-      <c r="F112">
-        <v>3085</v>
-      </c>
-      <c r="G112">
-        <v>4</v>
-      </c>
-      <c r="H112">
-        <v>2785</v>
-      </c>
-      <c r="I112">
-        <v>2784</v>
-      </c>
-      <c r="J112">
-        <v>1</v>
-      </c>
-      <c r="K112">
-        <v>0.90158627387504042</v>
-      </c>
-      <c r="L112">
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M112">
-        <v>0.25</v>
-      </c>
-      <c r="N112">
-        <f t="shared" si="9"/>
-        <v>0.68799407114624511</v>
-      </c>
-      <c r="O112">
-        <f t="shared" si="10"/>
-        <v>0.69652239179384534</v>
-      </c>
-      <c r="P112">
-        <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <f>AVERAGE(A103:A112)</f>
-        <v>4783</v>
-      </c>
-      <c r="B115">
-        <f>AVERAGE(B103:B112)</f>
-        <v>4052</v>
-      </c>
-      <c r="C115">
-        <f t="shared" ref="C115:P115" si="12">AVERAGE(C103:C112)</f>
-        <v>4003.6</v>
-      </c>
-      <c r="D115">
-        <f t="shared" si="12"/>
-        <v>48.4</v>
-      </c>
-      <c r="E115">
-        <f t="shared" si="12"/>
-        <v>3089</v>
-      </c>
-      <c r="F115">
-        <f t="shared" si="12"/>
-        <v>3085</v>
-      </c>
-      <c r="G115">
-        <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="H115">
-        <f t="shared" si="12"/>
-        <v>2785</v>
-      </c>
-      <c r="I115">
-        <f t="shared" si="12"/>
-        <v>2784</v>
-      </c>
-      <c r="J115">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="K115">
-        <f t="shared" si="12"/>
-        <v>0.9015862738750402</v>
-      </c>
-      <c r="L115">
-        <f t="shared" si="12"/>
-        <v>0.90243111831442469</v>
-      </c>
-      <c r="M115">
-        <f t="shared" si="12"/>
-        <v>0.25</v>
-      </c>
-      <c r="N115">
-        <f t="shared" si="12"/>
-        <v>0.68732088712359718</v>
-      </c>
-      <c r="O115">
-        <f t="shared" si="12"/>
-        <v>0.6953909500547758</v>
-      </c>
-      <c r="P115">
-        <f t="shared" si="12"/>
-        <v>2.1647058823529408E-2</v>
-      </c>
-      <c r="Q115" t="s">
+        <v>3.5518231244896302E-2</v>
+      </c>
+      <c r="Q105" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A116">
-        <f>AVERAGE(A3:A102)</f>
-        <v>1912.9</v>
-      </c>
-      <c r="B116">
-        <f t="shared" ref="B116:P116" si="13">AVERAGE(B3:B102)</f>
-        <v>1616.5</v>
-      </c>
-      <c r="C116">
-        <f t="shared" si="13"/>
-        <v>1589.34</v>
-      </c>
-      <c r="D116">
-        <f t="shared" si="13"/>
-        <v>27.16</v>
-      </c>
-      <c r="E116">
-        <f t="shared" si="13"/>
-        <v>1246.8900000000001</v>
-      </c>
-      <c r="F116">
-        <f t="shared" si="13"/>
-        <v>1245.1500000000001</v>
-      </c>
-      <c r="G116">
-        <f t="shared" si="13"/>
-        <v>1.74</v>
-      </c>
-      <c r="H116">
-        <f t="shared" si="13"/>
-        <v>1128.23</v>
-      </c>
-      <c r="I116">
-        <f t="shared" si="13"/>
-        <v>1127.3399999999999</v>
-      </c>
-      <c r="J116">
-        <f t="shared" si="13"/>
-        <v>0.89</v>
-      </c>
-      <c r="K116">
-        <f t="shared" si="13"/>
-        <v>0.90489731188596967</v>
-      </c>
-      <c r="L116">
-        <f t="shared" si="13"/>
-        <v>0.90544552828692626</v>
-      </c>
-      <c r="M116">
-        <f t="shared" si="13"/>
-        <v>0.40016666666666673</v>
-      </c>
-      <c r="N116">
-        <f t="shared" si="13"/>
-        <v>0.69798167731187843</v>
-      </c>
-      <c r="O116">
-        <f t="shared" si="13"/>
-        <v>0.70936400714902093</v>
-      </c>
-      <c r="P116">
-        <f t="shared" si="13"/>
-        <v>3.5518231244896302E-2</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -6500,4 +5900,660 @@
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87396B7F-5ACD-4C63-8F38-8C1E3CC3A8AE}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4783</v>
+      </c>
+      <c r="B2">
+        <v>4048</v>
+      </c>
+      <c r="C2">
+        <v>3997</v>
+      </c>
+      <c r="D2">
+        <v>51</v>
+      </c>
+      <c r="E2">
+        <v>3089</v>
+      </c>
+      <c r="F2">
+        <v>3085</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2785</v>
+      </c>
+      <c r="I2">
+        <v>2784</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L2">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M2">
+        <v>0.25</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:N11" si="0">H2/B2</f>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O2">
+        <f t="shared" ref="O2:O11" si="1">I2/C2</f>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P2">
+        <f t="shared" ref="P2:P11" si="2">J2/D2</f>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4783</v>
+      </c>
+      <c r="B3">
+        <v>4048</v>
+      </c>
+      <c r="C3">
+        <v>3997</v>
+      </c>
+      <c r="D3">
+        <v>51</v>
+      </c>
+      <c r="E3">
+        <v>3089</v>
+      </c>
+      <c r="F3">
+        <v>3085</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>2785</v>
+      </c>
+      <c r="I3">
+        <v>2784</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L3">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M3">
+        <v>0.25</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4783</v>
+      </c>
+      <c r="B4">
+        <v>4048</v>
+      </c>
+      <c r="C4">
+        <v>3997</v>
+      </c>
+      <c r="D4">
+        <v>51</v>
+      </c>
+      <c r="E4">
+        <v>3089</v>
+      </c>
+      <c r="F4">
+        <v>3085</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>2785</v>
+      </c>
+      <c r="I4">
+        <v>2784</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L4">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M4">
+        <v>0.25</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4783</v>
+      </c>
+      <c r="B5">
+        <v>4048</v>
+      </c>
+      <c r="C5">
+        <v>3997</v>
+      </c>
+      <c r="D5">
+        <v>51</v>
+      </c>
+      <c r="E5">
+        <v>3089</v>
+      </c>
+      <c r="F5">
+        <v>3085</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2785</v>
+      </c>
+      <c r="I5">
+        <v>2784</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L5">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M5">
+        <v>0.25</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4783</v>
+      </c>
+      <c r="B6">
+        <v>4048</v>
+      </c>
+      <c r="C6">
+        <v>3997</v>
+      </c>
+      <c r="D6">
+        <v>51</v>
+      </c>
+      <c r="E6">
+        <v>3089</v>
+      </c>
+      <c r="F6">
+        <v>3085</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2785</v>
+      </c>
+      <c r="I6">
+        <v>2784</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L6">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M6">
+        <v>0.25</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4783</v>
+      </c>
+      <c r="B7">
+        <v>4048</v>
+      </c>
+      <c r="C7">
+        <v>3997</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>3089</v>
+      </c>
+      <c r="F7">
+        <v>3085</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>2785</v>
+      </c>
+      <c r="I7">
+        <v>2784</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L7">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M7">
+        <v>0.25</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>4783</v>
+      </c>
+      <c r="B8">
+        <v>4088</v>
+      </c>
+      <c r="C8">
+        <v>4063</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>3089</v>
+      </c>
+      <c r="F8">
+        <v>3085</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>2785</v>
+      </c>
+      <c r="I8">
+        <v>2784</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L8">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M8">
+        <v>0.25</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>0.68126223091976512</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>0.6852079744031504</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="2"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4783</v>
+      </c>
+      <c r="B9">
+        <v>4048</v>
+      </c>
+      <c r="C9">
+        <v>3997</v>
+      </c>
+      <c r="D9">
+        <v>51</v>
+      </c>
+      <c r="E9">
+        <v>3089</v>
+      </c>
+      <c r="F9">
+        <v>3085</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>2785</v>
+      </c>
+      <c r="I9">
+        <v>2784</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L9">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M9">
+        <v>0.25</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>4783</v>
+      </c>
+      <c r="B10">
+        <v>4048</v>
+      </c>
+      <c r="C10">
+        <v>3997</v>
+      </c>
+      <c r="D10">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <v>3089</v>
+      </c>
+      <c r="F10">
+        <v>3085</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>2785</v>
+      </c>
+      <c r="I10">
+        <v>2784</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L10">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M10">
+        <v>0.25</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>4783</v>
+      </c>
+      <c r="B11">
+        <v>4048</v>
+      </c>
+      <c r="C11">
+        <v>3997</v>
+      </c>
+      <c r="D11">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>3089</v>
+      </c>
+      <c r="F11">
+        <v>3085</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>2785</v>
+      </c>
+      <c r="I11">
+        <v>2784</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0.90158627387504042</v>
+      </c>
+      <c r="L11">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M11">
+        <v>0.25</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>0.68799407114624511</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="1"/>
+        <v>0.69652239179384534</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f>AVERAGE(A2:A11)</f>
+        <v>4783</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ref="B13:P13" si="3">AVERAGE(B2:B11)</f>
+        <v>4052</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="3"/>
+        <v>4003.6</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>48.4</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>3089</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>3085</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="3"/>
+        <v>2785</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>2784</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="3"/>
+        <v>0.9015862738750402</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="3"/>
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="3"/>
+        <v>0.68732088712359718</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="3"/>
+        <v>0.6953909500547758</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="3"/>
+        <v>2.1647058823529408E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>